--- a/mlb_weather_professional_v5_2026_10_04.xlsx
+++ b/mlb_weather_professional_v5_2026_10_04.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="317">
   <si>
     <t>Date</t>
   </si>
@@ -371,10 +371,10 @@
     <t>GOOD DATA</t>
   </si>
   <si>
-    <t>🟢 10.2 mph Out to CF</t>
-  </si>
-  <si>
-    <t>🟢 7.4 mph Out to RF</t>
+    <t>🟢 10.3 mph Out to CF</t>
+  </si>
+  <si>
+    <t>🟢 7.5 mph Out to RF</t>
   </si>
   <si>
     <t>NW</t>
@@ -389,10 +389,10 @@
     <t>B+</t>
   </si>
   <si>
-    <t>Density 62 | Wind 72 | Temp 42 | Altitude 57 | Confidence 95%</t>
-  </si>
-  <si>
-    <t>Density 80 | Wind 62 | Temp 70 | Altitude 70 | Confidence 86%</t>
+    <t>Density 62 | Wind 72 | Temp 43 | Altitude 58 | Confidence 89%</t>
+  </si>
+  <si>
+    <t>Density 82 | Wind 61 | Temp 73 | Altitude 71 | Confidence 89%</t>
   </si>
   <si>
     <t>🟢 Good</t>
@@ -401,28 +401,34 @@
     <t>STABLE</t>
   </si>
   <si>
-    <t>1st-3rd: OUT TO CF +9.1 mph | 4th-5th: OUT TO CF +9.4 mph | 6th-7th: OUT TO CF +8.5 mph | 8th-9th: OUT TO CF +7.0 mph</t>
-  </si>
-  <si>
-    <t>1st-3rd: OUT TO RCF +6.0 mph | 4th-5th: OUT TO RCF +5.4 mph | 6th-7th: OUT TO RCF +3.7 mph | 8th-9th: LIGHT / VARIABLE -0.0 mph</t>
+    <t>SHIFTING</t>
+  </si>
+  <si>
+    <t>1st-3rd: OUT TO CF +9.3 mph | 4th-5th: OUT TO CF +8.9 mph | 6th-7th: OUT TO CF +8.5 mph | 8th-9th: OUT TO CF +6.6 mph</t>
+  </si>
+  <si>
+    <t>1st-3rd: OUT TO RCF +6.2 mph | 4th-5th: OUT TO RCF +4.8 mph | 6th-7th: OUT TO RF +2.5 mph | 8th-9th: CROSS LF → RF +0.1 mph</t>
   </si>
   <si>
     <t>MODEL_VERTICAL_PROFILE</t>
   </si>
   <si>
-    <t>FIRST RUN</t>
+    <t>IMPROVING RAPIDLY</t>
+  </si>
+  <si>
+    <t>2026-10-04 05:12:40 UTC</t>
+  </si>
+  <si>
+    <t>2026-10-04 05:12:50 UTC</t>
   </si>
   <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>2026-10-03 10:12:40 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-10-03 10:12:50 PM PDT</t>
+    <t>2026-10-04 04:58:50 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-10-04 04:59:00 PM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -902,24 +908,21 @@
     <t>08:00 PM PDT</t>
   </si>
   <si>
-    <t>2026-10-04 05:12:40 UTC</t>
-  </si>
-  <si>
-    <t>2026-10-04 05:12:50 UTC</t>
-  </si>
-  <si>
-    <t>2026-10-04T04:31:36+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-03T19:21:37+00:00</t>
+    <t>2026-10-04 23:58:50 UTC</t>
+  </si>
+  <si>
+    <t>2026-10-04 23:59:00 UTC</t>
+  </si>
+  <si>
+    <t>2026-10-04T22:56:49+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-04T18:26:40+00:00</t>
   </si>
   <si>
     <t>NWS 28.2%; GFS_HRRR 41.1%; ECMWF 16.5%; ICON 14.1%</t>
   </si>
   <si>
-    <t>NWS 30.0%; GFS_HRRR 35.0%; ECMWF 20.0%; ICON 15.0%</t>
-  </si>
-  <si>
     <t>YES</t>
   </si>
   <si>
@@ -947,7 +950,10 @@
     <t>CONSENSUS_DIRECTION_HELD_CONSTANT</t>
   </si>
   <si>
-    <t>NNW</t>
+    <t>WSW</t>
+  </si>
+  <si>
+    <t>WNW</t>
   </si>
   <si>
     <t>OUT TO CF</t>
@@ -956,7 +962,10 @@
     <t>OUT TO RCF</t>
   </si>
   <si>
-    <t>LIGHT / VARIABLE</t>
+    <t>OUT TO RF</t>
+  </si>
+  <si>
+    <t>CROSS LF → RF</t>
   </si>
   <si>
     <t>NEUTRAL</t>
@@ -1470,7 +1479,7 @@
     <col min="65" max="69" width="34.7109375" customWidth="1"/>
     <col min="70" max="70" width="31.7109375" customWidth="1"/>
     <col min="71" max="71" width="34.7109375" customWidth="1"/>
-    <col min="72" max="72" width="16.7109375" customWidth="1"/>
+    <col min="72" max="72" width="19.7109375" customWidth="1"/>
     <col min="73" max="73" width="34.7109375" customWidth="1"/>
     <col min="74" max="74" width="30.7109375" customWidth="1"/>
     <col min="75" max="77" width="34.7109375" customWidth="1"/>
@@ -1832,31 +1841,31 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>66.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="R2">
-        <v>51.2</v>
+        <v>47.5</v>
       </c>
       <c r="S2" t="s">
         <v>116</v>
       </c>
       <c r="T2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>118</v>
       </c>
       <c r="V2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W2">
+        <v>10.3</v>
+      </c>
+      <c r="X2">
         <v>8.300000000000001</v>
       </c>
-      <c r="W2">
-        <v>10.2</v>
-      </c>
-      <c r="X2">
-        <v>7.9</v>
-      </c>
       <c r="Y2">
-        <v>-0.5</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="s">
         <v>120</v>
@@ -1865,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>63</v>
+        <v>62.7</v>
       </c>
       <c r="AD2" t="s">
         <v>121</v>
@@ -1880,16 +1889,16 @@
         <v>6</v>
       </c>
       <c r="AH2">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AI2">
-        <v>94.7</v>
+        <v>89</v>
       </c>
       <c r="AJ2" t="s">
         <v>124</v>
       </c>
       <c r="AK2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AL2">
         <v>7</v>
@@ -1904,130 +1913,142 @@
         <v>100</v>
       </c>
       <c r="AP2">
-        <v>66.5</v>
+        <v>60.1</v>
       </c>
       <c r="AQ2">
         <v>0</v>
       </c>
       <c r="AR2">
-        <v>95.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AS2">
-        <v>97</v>
+        <v>97.2</v>
       </c>
       <c r="AT2">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="AU2" t="s">
         <v>125</v>
       </c>
       <c r="AV2">
-        <v>21</v>
+        <v>22.6</v>
       </c>
       <c r="AW2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX2">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AY2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AZ2">
-        <v>1.1857</v>
+        <v>1.185</v>
       </c>
       <c r="BA2">
-        <v>978</v>
+        <v>1015</v>
       </c>
       <c r="BB2">
-        <v>995.6</v>
+        <v>995.2</v>
       </c>
       <c r="BC2">
-        <v>46.1</v>
+        <v>42.8</v>
       </c>
       <c r="BD2">
-        <v>64.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="BE2">
-        <v>51.8</v>
+        <v>46.8</v>
       </c>
       <c r="BF2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BG2">
         <v>0.135</v>
       </c>
       <c r="BH2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BI2">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="BK2">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="BL2">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="BM2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN2">
+        <v>8.6</v>
+      </c>
+      <c r="BO2">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BP2">
+        <v>11.1</v>
+      </c>
+      <c r="BQ2">
+        <v>11.9</v>
+      </c>
+      <c r="BR2">
+        <v>10.7</v>
+      </c>
+      <c r="BS2">
         <v>8.699999999999999</v>
       </c>
-      <c r="BO2">
+      <c r="BT2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BU2">
+        <v>10.5</v>
+      </c>
+      <c r="BV2">
+        <v>0.3</v>
+      </c>
+      <c r="BW2">
+        <v>-0.3</v>
+      </c>
+      <c r="BX2">
+        <v>0</v>
+      </c>
+      <c r="BY2">
+        <v>0</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CA2">
+        <v>10.5</v>
+      </c>
+      <c r="CB2">
+        <v>-0.3</v>
+      </c>
+      <c r="CC2">
+        <v>0.3</v>
+      </c>
+      <c r="CD2">
+        <v>0</v>
+      </c>
+      <c r="CE2">
         <v>9.9</v>
       </c>
-      <c r="BP2">
-        <v>11.3</v>
-      </c>
-      <c r="BQ2">
-        <v>12.1</v>
-      </c>
-      <c r="BR2">
-        <v>10.9</v>
-      </c>
-      <c r="BS2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>129</v>
-      </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
-      <c r="BV2">
-        <v>0</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0</v>
-      </c>
-      <c r="BY2">
-        <v>0</v>
-      </c>
-      <c r="CA2">
-        <v>0</v>
-      </c>
-      <c r="CB2">
-        <v>0</v>
-      </c>
-      <c r="CC2">
-        <v>0</v>
-      </c>
-      <c r="CD2">
+      <c r="CF2">
+        <v>64.8</v>
+      </c>
+      <c r="CG2">
         <v>0</v>
       </c>
       <c r="CH2">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="CI2">
-        <v>64.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="CJ2">
         <v>0</v>
@@ -2039,22 +2060,22 @@
         <v>35</v>
       </c>
       <c r="CM2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="CN2">
         <v>0</v>
       </c>
       <c r="CO2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="CP2">
-        <v>8.300000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="CQ2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="CR2">
-        <v>41.1</v>
+        <v>62</v>
       </c>
       <c r="CS2">
         <v>5</v>
@@ -2107,40 +2128,40 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>95.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="R3">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="S3" t="s">
         <v>117</v>
       </c>
       <c r="T3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="U3" t="s">
         <v>119</v>
       </c>
       <c r="V3">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="W3">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X3">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Y3">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA3" t="s">
         <v>120</v>
       </c>
       <c r="AB3">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="AC3">
-        <v>63.8</v>
+        <v>64.2</v>
       </c>
       <c r="AD3" t="s">
         <v>121</v>
@@ -2152,31 +2173,31 @@
         <v>9</v>
       </c>
       <c r="AG3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI3">
-        <v>86.3</v>
+        <v>88.7</v>
       </c>
       <c r="AJ3" t="s">
         <v>124</v>
       </c>
       <c r="AK3">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AL3">
         <v>3</v>
       </c>
       <c r="AM3">
-        <v>87.2</v>
+        <v>76</v>
       </c>
       <c r="AN3">
         <v>2.3</v>
       </c>
       <c r="AO3">
-        <v>71.7</v>
+        <v>58.2</v>
       </c>
       <c r="AP3">
         <v>0</v>
@@ -2185,127 +2206,139 @@
         <v>0</v>
       </c>
       <c r="AR3">
-        <v>84.2</v>
+        <v>86.7</v>
       </c>
       <c r="AS3">
-        <v>96.40000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AV3">
-        <v>32.8</v>
+        <v>30.6</v>
       </c>
       <c r="AW3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX3">
-        <v>17.6</v>
+        <v>13.7</v>
       </c>
       <c r="AY3">
         <v>0.9</v>
       </c>
       <c r="AZ3">
-        <v>1.1246</v>
+        <v>1.1189</v>
       </c>
       <c r="BA3">
-        <v>2815</v>
+        <v>2999</v>
       </c>
       <c r="BB3">
-        <v>993.3</v>
+        <v>993.1</v>
       </c>
       <c r="BC3">
-        <v>52.3</v>
+        <v>52.7</v>
       </c>
       <c r="BD3">
+        <v>94</v>
+      </c>
+      <c r="BE3">
+        <v>27.2</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BG3">
+        <v>0.141</v>
+      </c>
+      <c r="BH3">
+        <v>5.5</v>
+      </c>
+      <c r="BI3">
+        <v>6.9</v>
+      </c>
+      <c r="BJ3">
+        <v>7.6</v>
+      </c>
+      <c r="BK3">
+        <v>8.4</v>
+      </c>
+      <c r="BL3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BM3">
+        <v>3.2</v>
+      </c>
+      <c r="BN3">
+        <v>4.2</v>
+      </c>
+      <c r="BO3">
+        <v>4.9</v>
+      </c>
+      <c r="BP3">
+        <v>5.6</v>
+      </c>
+      <c r="BQ3">
+        <v>6</v>
+      </c>
+      <c r="BR3">
+        <v>6.9</v>
+      </c>
+      <c r="BS3">
+        <v>4.3</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>130</v>
+      </c>
+      <c r="BU3">
+        <v>5.4</v>
+      </c>
+      <c r="BV3">
+        <v>2.6</v>
+      </c>
+      <c r="BW3">
+        <v>-0.3</v>
+      </c>
+      <c r="BX3">
+        <v>1</v>
+      </c>
+      <c r="BY3">
+        <v>-11.2</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>132</v>
+      </c>
+      <c r="CA3">
+        <v>5.4</v>
+      </c>
+      <c r="CB3">
+        <v>-0.3</v>
+      </c>
+      <c r="CC3">
+        <v>2.6</v>
+      </c>
+      <c r="CD3">
+        <v>1</v>
+      </c>
+      <c r="CE3">
+        <v>5.4</v>
+      </c>
+      <c r="CF3">
         <v>91.40000000000001</v>
       </c>
-      <c r="BE3">
-        <v>28</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>128</v>
-      </c>
-      <c r="BG3">
-        <v>0.142</v>
-      </c>
-      <c r="BH3">
-        <v>5.3</v>
-      </c>
-      <c r="BI3">
-        <v>6.6</v>
-      </c>
-      <c r="BJ3">
-        <v>7.3</v>
-      </c>
-      <c r="BK3">
-        <v>8.1</v>
-      </c>
-      <c r="BL3">
-        <v>8.5</v>
-      </c>
-      <c r="BM3">
-        <v>3.5</v>
-      </c>
-      <c r="BN3">
-        <v>4.6</v>
-      </c>
-      <c r="BO3">
-        <v>5.3</v>
-      </c>
-      <c r="BP3">
-        <v>6</v>
-      </c>
-      <c r="BQ3">
-        <v>6.5</v>
-      </c>
-      <c r="BR3">
-        <v>6.6</v>
-      </c>
-      <c r="BS3">
-        <v>4.6</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>129</v>
-      </c>
-      <c r="BU3">
-        <v>0</v>
-      </c>
-      <c r="BV3">
-        <v>0</v>
-      </c>
-      <c r="BW3">
-        <v>0</v>
-      </c>
-      <c r="BX3">
-        <v>0</v>
-      </c>
-      <c r="BY3">
-        <v>0</v>
-      </c>
-      <c r="CA3">
-        <v>0</v>
-      </c>
-      <c r="CB3">
-        <v>0</v>
-      </c>
-      <c r="CC3">
-        <v>0</v>
-      </c>
-      <c r="CD3">
-        <v>0</v>
+      <c r="CG3">
+        <v>0.6</v>
       </c>
       <c r="CH3">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="CI3">
-        <v>91.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="CJ3">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="CK3">
         <v>-0.26</v>
@@ -2314,22 +2347,22 @@
         <v>35</v>
       </c>
       <c r="CM3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="CN3">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="CO3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="CP3">
-        <v>22.2</v>
+        <v>13.8</v>
       </c>
       <c r="CQ3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="CR3">
-        <v>591.2</v>
+        <v>332.3</v>
       </c>
       <c r="CS3">
         <v>5</v>
@@ -2498,142 +2531,142 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>95</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>96</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AY1" s="1" t="s">
         <v>11</v>
@@ -2642,310 +2675,310 @@
         <v>12</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="EY1" s="1" t="s">
         <v>93</v>
@@ -2954,16 +2987,16 @@
         <v>92</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" spans="1:160">
@@ -2980,43 +3013,43 @@
         <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F2" t="s">
         <v>106</v>
       </c>
       <c r="G2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J2">
-        <v>41.1</v>
+        <v>62</v>
       </c>
       <c r="K2">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>5</v>
       </c>
       <c r="M2">
-        <v>0.62</v>
+        <v>1.16</v>
       </c>
       <c r="N2">
-        <v>0.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q2">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="R2">
         <v>100</v>
@@ -3025,28 +3058,28 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="U2">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="V2">
-        <v>15.9</v>
+        <v>16.4</v>
       </c>
       <c r="W2">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X2">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="Y2">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="Z2">
         <v>100</v>
       </c>
       <c r="AA2">
-        <v>74.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="AB2">
         <v>0</v>
@@ -3055,46 +3088,46 @@
         <v>100</v>
       </c>
       <c r="AD2">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AE2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AF2">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AG2">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="AH2">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="AI2">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="AJ2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AK2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN2">
         <v>1</v>
       </c>
       <c r="AO2">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AP2">
-        <v>95.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AQ2">
-        <v>77</v>
+        <v>75.2</v>
       </c>
       <c r="AR2">
         <v>0.82</v>
@@ -3127,22 +3160,22 @@
         <v>113</v>
       </c>
       <c r="BB2">
-        <v>66.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="BC2">
-        <v>60.1</v>
+        <v>62.1</v>
       </c>
       <c r="BD2">
-        <v>47.3</v>
+        <v>44.1</v>
       </c>
       <c r="BE2">
-        <v>51.2</v>
+        <v>47.5</v>
       </c>
       <c r="BF2">
-        <v>995.5</v>
+        <v>995.1</v>
       </c>
       <c r="BG2">
-        <v>1020.5</v>
+        <v>1020</v>
       </c>
       <c r="BH2">
         <v>0</v>
@@ -3154,208 +3187,208 @@
         <v>0</v>
       </c>
       <c r="BK2">
-        <v>82.40000000000001</v>
+        <v>112.3</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM2">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="BN2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO2">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="BP2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BQ2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BR2">
         <v>0.135</v>
       </c>
       <c r="BS2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="BU2">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="BV2">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="BW2">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="BX2">
         <v>6.2</v>
       </c>
       <c r="BY2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="BZ2">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="CA2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="CB2">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="CC2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="CD2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CE2">
+        <v>11.5</v>
+      </c>
+      <c r="CF2">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="CG2">
+        <v>10.6</v>
+      </c>
+      <c r="CH2">
+        <v>13.1</v>
+      </c>
+      <c r="CI2">
+        <v>10.6</v>
+      </c>
+      <c r="CJ2">
         <v>11.4</v>
       </c>
-      <c r="CF2">
-        <v>8.9</v>
-      </c>
-      <c r="CG2">
-        <v>10.8</v>
-      </c>
-      <c r="CH2">
-        <v>12.9</v>
-      </c>
-      <c r="CI2">
-        <v>10.2</v>
-      </c>
-      <c r="CJ2">
-        <v>11.6</v>
-      </c>
       <c r="CK2">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="CL2">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="CM2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="CN2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CO2">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="CP2">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="CQ2">
+        <v>12.7</v>
+      </c>
+      <c r="CR2">
+        <v>11.5</v>
+      </c>
+      <c r="CS2">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="CT2">
+        <v>11.9</v>
+      </c>
+      <c r="CU2">
         <v>12.5</v>
       </c>
-      <c r="CR2">
-        <v>11.3</v>
-      </c>
-      <c r="CS2">
-        <v>9.1</v>
-      </c>
-      <c r="CT2">
-        <v>11.8</v>
-      </c>
-      <c r="CU2">
-        <v>12.4</v>
-      </c>
       <c r="CV2">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="CW2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CX2">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="CY2">
-        <v>17.1</v>
+        <v>18</v>
       </c>
       <c r="CZ2">
-        <v>17.1</v>
+        <v>18</v>
       </c>
       <c r="DA2">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DB2" t="s">
         <v>118</v>
       </c>
       <c r="DC2">
-        <v>306.5</v>
+        <v>308.6</v>
       </c>
       <c r="DD2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="DE2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="DF2">
-        <v>96.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="DG2">
-        <v>96.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="DH2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DI2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="DJ2">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="DK2">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="DL2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="DM2">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DN2">
-        <v>-0.4</v>
+        <v>-0</v>
       </c>
       <c r="DO2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DP2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="DQ2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="DR2">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="DS2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="DT2">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DU2">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="DV2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="DW2">
         <v>8.300000000000001</v>
       </c>
-      <c r="DW2">
-        <v>7.9</v>
-      </c>
       <c r="DX2">
-        <v>-0.5</v>
+        <v>-0</v>
       </c>
       <c r="DY2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="EA2">
         <v>0.99</v>
@@ -3376,13 +3409,13 @@
         <v>0.1</v>
       </c>
       <c r="EG2">
-        <v>1.1824</v>
+        <v>1.1834</v>
       </c>
       <c r="EH2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="EI2">
-        <v>1069</v>
+        <v>1056</v>
       </c>
       <c r="EJ2" t="s">
         <v>110</v>
@@ -3391,61 +3424,61 @@
         <v>111</v>
       </c>
       <c r="EL2">
-        <v>78.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="EM2">
         <v>4</v>
       </c>
       <c r="EN2">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="EO2">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="EP2">
         <v>0</v>
       </c>
       <c r="EQ2">
-        <v>1.068</v>
+        <v>1.069</v>
       </c>
       <c r="ER2">
-        <v>77.2</v>
+        <v>77.7</v>
       </c>
       <c r="ES2">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="ET2">
         <v>60.5</v>
       </c>
       <c r="EU2">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
       <c r="EV2">
-        <v>69</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="EW2">
         <v>0</v>
       </c>
       <c r="EX2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="EY2">
-        <v>4.1</v>
+        <v>15.6</v>
       </c>
       <c r="EZ2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="FA2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="FB2">
-        <v>66.2</v>
+        <v>68.3</v>
       </c>
       <c r="FC2">
         <v>10</v>
       </c>
       <c r="FD2">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="3" spans="1:160">
@@ -3462,43 +3495,43 @@
         <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J3">
-        <v>41.1</v>
+        <v>62</v>
       </c>
       <c r="K3">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>5</v>
       </c>
       <c r="M3">
-        <v>0.75</v>
+        <v>1.52</v>
       </c>
       <c r="N3">
-        <v>1.05</v>
+        <v>0.64</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="Q3">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="R3">
         <v>100</v>
@@ -3507,28 +3540,28 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="U3">
-        <v>13.8</v>
+        <v>13.1</v>
       </c>
       <c r="V3">
-        <v>16.3</v>
+        <v>15.4</v>
       </c>
       <c r="W3">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="X3">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="Z3">
         <v>100</v>
       </c>
       <c r="AA3">
-        <v>80.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AB3">
         <v>0</v>
@@ -3537,46 +3570,46 @@
         <v>100</v>
       </c>
       <c r="AD3">
-        <v>96.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="AE3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AF3">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AG3">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="AH3">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="AI3">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="AJ3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AK3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN3">
         <v>1</v>
       </c>
       <c r="AO3">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AP3">
-        <v>93.8</v>
+        <v>89</v>
       </c>
       <c r="AQ3">
-        <v>77</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AR3">
         <v>0.82</v>
@@ -3612,19 +3645,19 @@
         <v>65.5</v>
       </c>
       <c r="BC3">
-        <v>58.6</v>
+        <v>61.7</v>
       </c>
       <c r="BD3">
-        <v>46.1</v>
+        <v>42.8</v>
       </c>
       <c r="BE3">
-        <v>50.6</v>
+        <v>46.3</v>
       </c>
       <c r="BF3">
-        <v>995.5</v>
+        <v>995</v>
       </c>
       <c r="BG3">
-        <v>1020.4</v>
+        <v>1019.9</v>
       </c>
       <c r="BH3">
         <v>0</v>
@@ -3636,208 +3669,208 @@
         <v>0</v>
       </c>
       <c r="BK3">
-        <v>89.5</v>
+        <v>123.1</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM3">
+        <v>10.4</v>
+      </c>
+      <c r="BN3">
+        <v>8.9</v>
+      </c>
+      <c r="BO3">
         <v>11</v>
       </c>
-      <c r="BN3">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="BO3">
-        <v>11.6</v>
-      </c>
       <c r="BP3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BQ3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BR3">
         <v>0.135</v>
       </c>
       <c r="BS3">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="BT3">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="BU3">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="BV3">
+        <v>13.3</v>
+      </c>
+      <c r="BW3">
         <v>14</v>
       </c>
-      <c r="BW3">
-        <v>14.8</v>
-      </c>
       <c r="BX3">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BY3">
+        <v>7.6</v>
+      </c>
+      <c r="BZ3">
+        <v>6.1</v>
+      </c>
+      <c r="CA3">
+        <v>7.6</v>
+      </c>
+      <c r="CB3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CC3">
         <v>8</v>
       </c>
-      <c r="BZ3">
-        <v>6.4</v>
-      </c>
-      <c r="CA3">
-        <v>8.1</v>
-      </c>
-      <c r="CB3">
-        <v>10.3</v>
-      </c>
-      <c r="CC3">
-        <v>8.300000000000001</v>
-      </c>
       <c r="CD3">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="CE3">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
       <c r="CF3">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="CG3">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="CH3">
-        <v>13.2</v>
+        <v>12.6</v>
       </c>
       <c r="CI3">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="CJ3">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="CK3">
-        <v>14.2</v>
+        <v>13.4</v>
       </c>
       <c r="CL3">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
       <c r="CM3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="CN3">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CO3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CP3">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="CQ3">
+        <v>12.2</v>
+      </c>
+      <c r="CR3">
+        <v>11</v>
+      </c>
+      <c r="CS3">
+        <v>8.9</v>
+      </c>
+      <c r="CT3">
+        <v>11.4</v>
+      </c>
+      <c r="CU3">
+        <v>12.1</v>
+      </c>
+      <c r="CV3">
         <v>12.9</v>
       </c>
-      <c r="CR3">
-        <v>11.6</v>
-      </c>
-      <c r="CS3">
-        <v>9.4</v>
-      </c>
-      <c r="CT3">
-        <v>12</v>
-      </c>
-      <c r="CU3">
-        <v>12.7</v>
-      </c>
-      <c r="CV3">
-        <v>13.6</v>
-      </c>
       <c r="CW3">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="CX3">
-        <v>21.6</v>
+        <v>20.2</v>
       </c>
       <c r="CY3">
-        <v>17.7</v>
+        <v>16.6</v>
       </c>
       <c r="CZ3">
-        <v>17.7</v>
+        <v>16.6</v>
       </c>
       <c r="DA3">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="DB3" t="s">
         <v>118</v>
       </c>
       <c r="DC3">
-        <v>309.4</v>
+        <v>310.3</v>
       </c>
       <c r="DD3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="DE3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="DF3">
-        <v>94.8</v>
+        <v>96</v>
       </c>
       <c r="DG3">
-        <v>94.8</v>
+        <v>96</v>
       </c>
       <c r="DH3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DI3">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="DJ3">
+        <v>0.2</v>
+      </c>
+      <c r="DK3">
+        <v>10.4</v>
+      </c>
+      <c r="DL3">
+        <v>8.4</v>
+      </c>
+      <c r="DM3">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="DN3">
         <v>0.3</v>
       </c>
-      <c r="DK3">
-        <v>11</v>
-      </c>
-      <c r="DL3">
+      <c r="DO3">
         <v>8.9</v>
       </c>
-      <c r="DM3">
-        <v>9</v>
-      </c>
-      <c r="DN3">
-        <v>0.1</v>
-      </c>
-      <c r="DO3">
-        <v>9.300000000000001</v>
-      </c>
       <c r="DP3">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="DQ3">
+        <v>7.4</v>
+      </c>
+      <c r="DR3">
+        <v>10.4</v>
+      </c>
+      <c r="DS3">
+        <v>8.4</v>
+      </c>
+      <c r="DT3">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="DU3">
+        <v>9.9</v>
+      </c>
+      <c r="DV3">
         <v>7.7</v>
       </c>
-      <c r="DR3">
-        <v>11</v>
-      </c>
-      <c r="DS3">
+      <c r="DW3">
+        <v>8.1</v>
+      </c>
+      <c r="DX3">
+        <v>0.3</v>
+      </c>
+      <c r="DY3">
         <v>8.9</v>
       </c>
-      <c r="DT3">
-        <v>9</v>
-      </c>
-      <c r="DU3">
-        <v>10.5</v>
-      </c>
-      <c r="DV3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="DW3">
-        <v>8.4</v>
-      </c>
-      <c r="DX3">
-        <v>0.1</v>
-      </c>
-      <c r="DY3">
-        <v>9.4</v>
-      </c>
       <c r="DZ3">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="EA3">
         <v>0.99</v>
@@ -3861,10 +3894,10 @@
         <v>1.1839</v>
       </c>
       <c r="EH3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="EI3">
-        <v>1030</v>
+        <v>1047</v>
       </c>
       <c r="EJ3" t="s">
         <v>110</v>
@@ -3873,61 +3906,61 @@
         <v>111</v>
       </c>
       <c r="EL3">
-        <v>78.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="EM3">
         <v>3.9</v>
       </c>
       <c r="EN3">
-        <v>23</v>
+        <v>21.8</v>
       </c>
       <c r="EO3">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="EP3">
         <v>0</v>
       </c>
       <c r="EQ3">
-        <v>1.069</v>
+        <v>1.066</v>
       </c>
       <c r="ER3">
-        <v>77.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="ES3">
-        <v>77.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="ET3">
-        <v>60.6</v>
+        <v>60.2</v>
       </c>
       <c r="EU3">
-        <v>52.3</v>
+        <v>51.9</v>
       </c>
       <c r="EV3">
-        <v>67.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="EW3">
         <v>0</v>
       </c>
       <c r="EX3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="EY3">
-        <v>6.2</v>
+        <v>13.4</v>
       </c>
       <c r="EZ3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="FA3">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="FB3">
-        <v>65.8</v>
+        <v>68</v>
       </c>
       <c r="FC3">
         <v>10</v>
       </c>
       <c r="FD3">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="4" spans="1:160">
@@ -3944,43 +3977,43 @@
         <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J4">
-        <v>41.1</v>
+        <v>62</v>
       </c>
       <c r="K4">
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>5</v>
       </c>
       <c r="M4">
-        <v>1.19</v>
+        <v>2.09</v>
       </c>
       <c r="N4">
-        <v>0.57</v>
+        <v>0.83</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>8.9</v>
+        <v>4</v>
       </c>
       <c r="Q4">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3989,28 +4022,28 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="U4">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="V4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="W4">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X4">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="Z4">
         <v>100</v>
       </c>
       <c r="AA4">
-        <v>55.1</v>
+        <v>50.8</v>
       </c>
       <c r="AB4">
         <v>0</v>
@@ -4019,46 +4052,46 @@
         <v>100</v>
       </c>
       <c r="AD4">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AE4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AF4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG4">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AH4">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="AI4">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="AJ4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AK4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN4">
         <v>1</v>
       </c>
       <c r="AO4">
-        <v>6.4</v>
+        <v>10.8</v>
       </c>
       <c r="AP4">
-        <v>95.2</v>
+        <v>89.8</v>
       </c>
       <c r="AQ4">
-        <v>74.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AR4">
         <v>0.82</v>
@@ -4091,25 +4124,25 @@
         <v>113</v>
       </c>
       <c r="BB4">
-        <v>63.6</v>
+        <v>64.8</v>
       </c>
       <c r="BC4">
-        <v>57.2</v>
+        <v>60.6</v>
       </c>
       <c r="BD4">
-        <v>44.8</v>
+        <v>41.1</v>
       </c>
       <c r="BE4">
-        <v>51.8</v>
+        <v>45.5</v>
       </c>
       <c r="BF4">
-        <v>995.7</v>
+        <v>995.3</v>
       </c>
       <c r="BG4">
-        <v>1020.8</v>
+        <v>1020.2</v>
       </c>
       <c r="BH4">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="BI4">
         <v>0</v>
@@ -4118,88 +4151,88 @@
         <v>0</v>
       </c>
       <c r="BK4">
-        <v>85.2</v>
+        <v>129.9</v>
       </c>
       <c r="BL4">
         <v>0</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="BN4">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BO4">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="BP4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BQ4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BR4">
         <v>0.135</v>
       </c>
       <c r="BS4">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BT4">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="BU4">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="BV4">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="BW4">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="BX4">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BY4">
         <v>7.3</v>
       </c>
       <c r="BZ4">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="CA4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB4">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="CC4">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="CD4">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="CE4">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="CF4">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CG4">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CH4">
         <v>12</v>
       </c>
       <c r="CI4">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="CJ4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CK4">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="CL4">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="CM4">
         <v>6.5</v>
@@ -4208,112 +4241,112 @@
         <v>8.4</v>
       </c>
       <c r="CO4">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="CP4">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="CQ4">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="CR4">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="CS4">
         <v>8.5</v>
       </c>
       <c r="CT4">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="CU4">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="CV4">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="CW4">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="CX4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CY4">
-        <v>16.4</v>
+        <v>15.6</v>
       </c>
       <c r="CZ4">
-        <v>16.4</v>
+        <v>15.6</v>
       </c>
       <c r="DA4">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="DB4" t="s">
         <v>118</v>
       </c>
       <c r="DC4">
-        <v>312.8</v>
+        <v>308</v>
       </c>
       <c r="DD4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="DE4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="DF4">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="DG4">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="DH4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DI4">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="DJ4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DK4">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="DL4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DM4">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="DN4">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="DO4">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="DP4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="DQ4">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="DR4">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="DS4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DT4">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="DU4">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="DV4">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="DW4">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="DX4">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="DY4">
         <v>8.5</v>
@@ -4325,7 +4358,7 @@
         <v>0.99</v>
       </c>
       <c r="EB4">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="EC4">
         <v>0.86</v>
@@ -4340,13 +4373,13 @@
         <v>0.1</v>
       </c>
       <c r="EG4">
-        <v>1.1888</v>
+        <v>1.1861</v>
       </c>
       <c r="EH4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="EI4">
-        <v>896</v>
+        <v>991</v>
       </c>
       <c r="EJ4" t="s">
         <v>110</v>
@@ -4358,13 +4391,13 @@
         <v>76.09999999999999</v>
       </c>
       <c r="EM4">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="EN4">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="EO4">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="EP4">
         <v>0</v>
@@ -4373,43 +4406,43 @@
         <v>1.063</v>
       </c>
       <c r="ER4">
-        <v>75.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="ES4">
-        <v>74.8</v>
+        <v>75.3</v>
       </c>
       <c r="ET4">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="EU4">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="EV4">
+        <v>68.8</v>
+      </c>
+      <c r="EW4">
+        <v>0</v>
+      </c>
+      <c r="EX4" t="s">
+        <v>133</v>
+      </c>
+      <c r="EY4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="EZ4" t="s">
+        <v>133</v>
+      </c>
+      <c r="FA4">
+        <v>62</v>
+      </c>
+      <c r="FB4">
         <v>66.8</v>
-      </c>
-      <c r="EW4">
-        <v>0</v>
-      </c>
-      <c r="EX4" t="s">
-        <v>130</v>
-      </c>
-      <c r="EY4">
-        <v>3.4</v>
-      </c>
-      <c r="EZ4" t="s">
-        <v>130</v>
-      </c>
-      <c r="FA4">
-        <v>63</v>
-      </c>
-      <c r="FB4">
-        <v>64</v>
       </c>
       <c r="FC4">
         <v>10</v>
       </c>
       <c r="FD4">
-        <v>10</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="5" spans="1:160">
@@ -4426,43 +4459,43 @@
         <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J5">
-        <v>41.1</v>
+        <v>62</v>
       </c>
       <c r="K5">
-        <v>17.8</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="N5">
-        <v>0.25</v>
+        <v>0.73</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>8.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="Q5">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -4471,28 +4504,28 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="U5">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="V5">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="W5">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="X5">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="Y5">
-        <v>11.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z5">
         <v>100</v>
       </c>
       <c r="AA5">
-        <v>26.6</v>
+        <v>0.2</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -4501,46 +4534,46 @@
         <v>100</v>
       </c>
       <c r="AD5">
-        <v>96.8</v>
+        <v>98.2</v>
       </c>
       <c r="AE5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AF5">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AG5">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AH5">
-        <v>11.4</v>
+        <v>9.5</v>
       </c>
       <c r="AI5">
-        <v>12.9</v>
+        <v>10.8</v>
       </c>
       <c r="AJ5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AK5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN5">
         <v>1</v>
       </c>
       <c r="AO5">
-        <v>6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AP5">
-        <v>92.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AQ5">
-        <v>70.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AR5">
         <v>0.82</v>
@@ -4573,25 +4606,25 @@
         <v>113</v>
       </c>
       <c r="BB5">
-        <v>60.8</v>
+        <v>62.7</v>
       </c>
       <c r="BC5">
-        <v>55.1</v>
+        <v>58.4</v>
       </c>
       <c r="BD5">
-        <v>44.4</v>
+        <v>41.1</v>
       </c>
       <c r="BE5">
-        <v>56.3</v>
+        <v>48.2</v>
       </c>
       <c r="BF5">
-        <v>996.2</v>
+        <v>995.6</v>
       </c>
       <c r="BG5">
-        <v>1021.4</v>
+        <v>1020.7</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="BI5">
         <v>0</v>
@@ -4600,208 +4633,208 @@
         <v>0</v>
       </c>
       <c r="BK5">
-        <v>75.2</v>
+        <v>118.2</v>
       </c>
       <c r="BL5">
         <v>0</v>
       </c>
       <c r="BM5">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="BN5">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BO5">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="BP5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BQ5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BR5">
         <v>0.135</v>
       </c>
       <c r="BS5">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BT5">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="BU5">
+        <v>8.9</v>
+      </c>
+      <c r="BV5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BW5">
+        <v>10.3</v>
+      </c>
+      <c r="BX5">
+        <v>4.3</v>
+      </c>
+      <c r="BY5">
+        <v>5.6</v>
+      </c>
+      <c r="BZ5">
+        <v>4.5</v>
+      </c>
+      <c r="CA5">
+        <v>5.6</v>
+      </c>
+      <c r="CB5">
+        <v>7.2</v>
+      </c>
+      <c r="CC5">
+        <v>5.9</v>
+      </c>
+      <c r="CD5">
+        <v>6.4</v>
+      </c>
+      <c r="CE5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CF5">
+        <v>6.7</v>
+      </c>
+      <c r="CG5">
+        <v>7.4</v>
+      </c>
+      <c r="CH5">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="CI5">
+        <v>7.6</v>
+      </c>
+      <c r="CJ5">
+        <v>8</v>
+      </c>
+      <c r="CK5">
+        <v>9.9</v>
+      </c>
+      <c r="CL5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CM5">
+        <v>5</v>
+      </c>
+      <c r="CN5">
+        <v>6.5</v>
+      </c>
+      <c r="CO5">
+        <v>7.4</v>
+      </c>
+      <c r="CP5">
+        <v>8.4</v>
+      </c>
+      <c r="CQ5">
+        <v>9</v>
+      </c>
+      <c r="CR5">
+        <v>8.1</v>
+      </c>
+      <c r="CS5">
+        <v>6.6</v>
+      </c>
+      <c r="CT5">
+        <v>8.4</v>
+      </c>
+      <c r="CU5">
+        <v>8.9</v>
+      </c>
+      <c r="CV5">
         <v>9.5</v>
       </c>
-      <c r="BV5">
-        <v>10.4</v>
-      </c>
-      <c r="BW5">
-        <v>11</v>
-      </c>
-      <c r="BX5">
-        <v>4.5</v>
-      </c>
-      <c r="BY5">
-        <v>6</v>
-      </c>
-      <c r="BZ5">
+      <c r="CW5">
+        <v>6.5</v>
+      </c>
+      <c r="CX5">
+        <v>13.9</v>
+      </c>
+      <c r="CY5">
+        <v>11.4</v>
+      </c>
+      <c r="CZ5">
+        <v>11.4</v>
+      </c>
+      <c r="DA5">
         <v>4.9</v>
-      </c>
-      <c r="CA5">
-        <v>5.9</v>
-      </c>
-      <c r="CB5">
-        <v>7.7</v>
-      </c>
-      <c r="CC5">
-        <v>6.3</v>
-      </c>
-      <c r="CD5">
-        <v>6.7</v>
-      </c>
-      <c r="CE5">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="CF5">
-        <v>7.2</v>
-      </c>
-      <c r="CG5">
-        <v>7.7</v>
-      </c>
-      <c r="CH5">
-        <v>9.9</v>
-      </c>
-      <c r="CI5">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="CJ5">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="CK5">
-        <v>10.5</v>
-      </c>
-      <c r="CL5">
-        <v>8.9</v>
-      </c>
-      <c r="CM5">
-        <v>5.3</v>
-      </c>
-      <c r="CN5">
-        <v>6.9</v>
-      </c>
-      <c r="CO5">
-        <v>7.8</v>
-      </c>
-      <c r="CP5">
-        <v>8.9</v>
-      </c>
-      <c r="CQ5">
-        <v>9.6</v>
-      </c>
-      <c r="CR5">
-        <v>8.6</v>
-      </c>
-      <c r="CS5">
-        <v>7</v>
-      </c>
-      <c r="CT5">
-        <v>9</v>
-      </c>
-      <c r="CU5">
-        <v>9.5</v>
-      </c>
-      <c r="CV5">
-        <v>10.1</v>
-      </c>
-      <c r="CW5">
-        <v>7</v>
-      </c>
-      <c r="CX5">
-        <v>19.3</v>
-      </c>
-      <c r="CY5">
-        <v>15.8</v>
-      </c>
-      <c r="CZ5">
-        <v>15.8</v>
-      </c>
-      <c r="DA5">
-        <v>8.800000000000001</v>
       </c>
       <c r="DB5" t="s">
         <v>118</v>
       </c>
       <c r="DC5">
-        <v>311.4</v>
+        <v>310</v>
       </c>
       <c r="DD5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="DE5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="DF5">
-        <v>95</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="DG5">
-        <v>95</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="DH5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DI5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="DJ5">
+        <v>0.5</v>
+      </c>
+      <c r="DK5">
+        <v>7.7</v>
+      </c>
+      <c r="DL5">
+        <v>6.2</v>
+      </c>
+      <c r="DM5">
+        <v>6.4</v>
+      </c>
+      <c r="DN5">
+        <v>0.1</v>
+      </c>
+      <c r="DO5">
+        <v>6.5</v>
+      </c>
+      <c r="DP5">
+        <v>5.3</v>
+      </c>
+      <c r="DQ5">
+        <v>5.4</v>
+      </c>
+      <c r="DR5">
+        <v>7.7</v>
+      </c>
+      <c r="DS5">
+        <v>6.2</v>
+      </c>
+      <c r="DT5">
+        <v>6.4</v>
+      </c>
+      <c r="DU5">
+        <v>7.3</v>
+      </c>
+      <c r="DV5">
+        <v>5.7</v>
+      </c>
+      <c r="DW5">
+        <v>5.9</v>
+      </c>
+      <c r="DX5">
         <v>0.2</v>
       </c>
-      <c r="DK5">
-        <v>8.1</v>
-      </c>
-      <c r="DL5">
-        <v>6.5</v>
-      </c>
-      <c r="DM5">
-        <v>6.9</v>
-      </c>
-      <c r="DN5">
-        <v>0.4</v>
-      </c>
-      <c r="DO5">
-        <v>7</v>
-      </c>
-      <c r="DP5">
-        <v>5.5</v>
-      </c>
-      <c r="DQ5">
-        <v>5.9</v>
-      </c>
-      <c r="DR5">
-        <v>8.1</v>
-      </c>
-      <c r="DS5">
-        <v>6.5</v>
-      </c>
-      <c r="DT5">
-        <v>6.9</v>
-      </c>
-      <c r="DU5">
-        <v>7.8</v>
-      </c>
-      <c r="DV5">
-        <v>6</v>
-      </c>
-      <c r="DW5">
-        <v>6.4</v>
-      </c>
-      <c r="DX5">
-        <v>0.4</v>
-      </c>
       <c r="DY5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="DZ5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="EA5">
         <v>0.99</v>
@@ -4822,13 +4855,13 @@
         <v>0.1</v>
       </c>
       <c r="EG5">
-        <v>1.1956</v>
+        <v>1.1912</v>
       </c>
       <c r="EH5" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="EI5">
-        <v>700</v>
+        <v>842</v>
       </c>
       <c r="EJ5" t="s">
         <v>110</v>
@@ -4837,61 +4870,61 @@
         <v>111</v>
       </c>
       <c r="EL5">
-        <v>71.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="EM5">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="EN5">
-        <v>17.1</v>
+        <v>16.1</v>
       </c>
       <c r="EO5">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="EP5">
         <v>0</v>
       </c>
       <c r="EQ5">
-        <v>1.052</v>
+        <v>1.049</v>
       </c>
       <c r="ER5">
-        <v>71.3</v>
+        <v>70</v>
       </c>
       <c r="ES5">
-        <v>70.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="ET5">
-        <v>57.9</v>
+        <v>57.7</v>
       </c>
       <c r="EU5">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="EV5">
-        <v>64.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="EW5">
         <v>0</v>
       </c>
       <c r="EX5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="EY5">
-        <v>8.300000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="EZ5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="FA5">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="FB5">
-        <v>60.7</v>
+        <v>63.2</v>
       </c>
       <c r="FC5">
         <v>10</v>
       </c>
       <c r="FD5">
-        <v>6.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:160">
@@ -4908,43 +4941,43 @@
         <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F6" t="s">
         <v>107</v>
       </c>
       <c r="G6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J6">
-        <v>591.2</v>
+        <v>332.3</v>
       </c>
       <c r="K6">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>2.21</v>
+        <v>1.17</v>
       </c>
       <c r="N6">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -4953,7 +4986,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="U6">
         <v>9.800000000000001</v>
@@ -4962,16 +4995,16 @@
         <v>11.1</v>
       </c>
       <c r="W6">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="X6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>7.9</v>
       </c>
       <c r="Z6">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="AA6">
         <v>0</v>
@@ -4983,52 +5016,52 @@
         <v>100</v>
       </c>
       <c r="AD6">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AF6">
         <v>2.4</v>
       </c>
       <c r="AG6">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="AH6">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI6">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="AJ6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AK6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN6">
         <v>1</v>
       </c>
       <c r="AO6">
-        <v>12.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP6">
-        <v>89.5</v>
+        <v>88.5</v>
       </c>
       <c r="AQ6">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="AR6">
         <v>0.78</v>
       </c>
       <c r="AS6">
-        <v>0.8169999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AT6">
         <v>10</v>
@@ -5055,235 +5088,235 @@
         <v>113</v>
       </c>
       <c r="BB6">
-        <v>95.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="BC6">
-        <v>90.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="BD6">
-        <v>50.7</v>
+        <v>53.6</v>
       </c>
       <c r="BE6">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="BF6">
-        <v>992.9</v>
+        <v>992.7</v>
       </c>
       <c r="BG6">
-        <v>1010.6</v>
+        <v>1010.4</v>
       </c>
       <c r="BH6">
         <v>0</v>
       </c>
       <c r="BI6">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="BJ6">
         <v>0</v>
       </c>
       <c r="BK6">
-        <v>131.5</v>
+        <v>140.9</v>
       </c>
       <c r="BL6">
         <v>0</v>
       </c>
       <c r="BM6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN6">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="BO6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BQ6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BR6">
         <v>0.141</v>
       </c>
       <c r="BS6">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="BT6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU6">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BV6">
+        <v>10.7</v>
+      </c>
+      <c r="BW6">
+        <v>11.3</v>
+      </c>
+      <c r="BX6">
+        <v>2.9</v>
+      </c>
+      <c r="BY6">
+        <v>5.4</v>
+      </c>
+      <c r="BZ6">
+        <v>5.6</v>
+      </c>
+      <c r="CA6">
+        <v>3.8</v>
+      </c>
+      <c r="CB6">
+        <v>7.1</v>
+      </c>
+      <c r="CC6">
+        <v>7.4</v>
+      </c>
+      <c r="CD6">
+        <v>4.4</v>
+      </c>
+      <c r="CE6">
+        <v>8</v>
+      </c>
+      <c r="CF6">
+        <v>8.5</v>
+      </c>
+      <c r="CG6">
+        <v>5.1</v>
+      </c>
+      <c r="CH6">
+        <v>9.1</v>
+      </c>
+      <c r="CI6">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="CJ6">
+        <v>5.5</v>
+      </c>
+      <c r="CK6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CL6">
         <v>10.5</v>
       </c>
-      <c r="BW6">
-        <v>11.1</v>
-      </c>
-      <c r="BX6">
-        <v>2.7</v>
-      </c>
-      <c r="BY6">
-        <v>5.3</v>
-      </c>
-      <c r="BZ6">
-        <v>5.5</v>
-      </c>
-      <c r="CA6">
-        <v>3.6</v>
-      </c>
-      <c r="CB6">
-        <v>6.9</v>
-      </c>
-      <c r="CC6">
-        <v>7.3</v>
-      </c>
-      <c r="CD6">
-        <v>4.2</v>
-      </c>
-      <c r="CE6">
-        <v>7.8</v>
-      </c>
-      <c r="CF6">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="CG6">
-        <v>4.9</v>
-      </c>
-      <c r="CH6">
-        <v>8.9</v>
-      </c>
-      <c r="CI6">
+      <c r="CM6">
+        <v>4.7</v>
+      </c>
+      <c r="CN6">
+        <v>6.1</v>
+      </c>
+      <c r="CO6">
+        <v>7</v>
+      </c>
+      <c r="CP6">
+        <v>8</v>
+      </c>
+      <c r="CQ6">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="CR6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CS6">
+        <v>6.2</v>
+      </c>
+      <c r="CT6">
+        <v>9.1</v>
+      </c>
+      <c r="CU6">
         <v>9.6</v>
       </c>
-      <c r="CJ6">
-        <v>5.3</v>
-      </c>
-      <c r="CK6">
-        <v>9.6</v>
-      </c>
-      <c r="CL6">
+      <c r="CV6">
         <v>10.4</v>
       </c>
-      <c r="CM6">
-        <v>4.5</v>
-      </c>
-      <c r="CN6">
-        <v>6</v>
-      </c>
-      <c r="CO6">
-        <v>6.8</v>
-      </c>
-      <c r="CP6">
-        <v>7.8</v>
-      </c>
-      <c r="CQ6">
-        <v>8.4</v>
-      </c>
-      <c r="CR6">
-        <v>8.6</v>
-      </c>
-      <c r="CS6">
-        <v>6</v>
-      </c>
-      <c r="CT6">
-        <v>9</v>
-      </c>
-      <c r="CU6">
-        <v>9.5</v>
-      </c>
-      <c r="CV6">
-        <v>10.2</v>
-      </c>
       <c r="CW6">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="CX6">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="CY6">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="CZ6">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="DA6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="DB6" t="s">
         <v>119</v>
       </c>
       <c r="DC6">
-        <v>231.5</v>
+        <v>230.5</v>
       </c>
       <c r="DD6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="DE6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="DF6">
-        <v>94.3</v>
+        <v>96.5</v>
       </c>
       <c r="DG6">
-        <v>94.3</v>
+        <v>96.5</v>
       </c>
       <c r="DH6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DI6">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="DJ6">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="DK6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="DL6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="DM6">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="DN6">
+        <v>3.5</v>
+      </c>
+      <c r="DO6">
+        <v>6.4</v>
+      </c>
+      <c r="DP6">
         <v>3.6</v>
       </c>
-      <c r="DO6">
+      <c r="DQ6">
+        <v>6.9</v>
+      </c>
+      <c r="DR6">
+        <v>7.8</v>
+      </c>
+      <c r="DS6">
+        <v>4.4</v>
+      </c>
+      <c r="DT6">
+        <v>8.4</v>
+      </c>
+      <c r="DU6">
+        <v>7.1</v>
+      </c>
+      <c r="DV6">
+        <v>3.9</v>
+      </c>
+      <c r="DW6">
+        <v>7.5</v>
+      </c>
+      <c r="DX6">
+        <v>3.5</v>
+      </c>
+      <c r="DY6">
         <v>6.2</v>
       </c>
-      <c r="DP6">
-        <v>3.4</v>
-      </c>
-      <c r="DQ6">
-        <v>6.8</v>
-      </c>
-      <c r="DR6">
-        <v>7.6</v>
-      </c>
-      <c r="DS6">
-        <v>4.2</v>
-      </c>
-      <c r="DT6">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="DU6">
-        <v>7</v>
-      </c>
-      <c r="DV6">
-        <v>3.7</v>
-      </c>
-      <c r="DW6">
-        <v>7.4</v>
-      </c>
-      <c r="DX6">
-        <v>3.6</v>
-      </c>
-      <c r="DY6">
-        <v>6</v>
-      </c>
       <c r="DZ6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="EA6">
         <v>0.96</v>
@@ -5304,13 +5337,13 @@
         <v>0.12</v>
       </c>
       <c r="EG6">
-        <v>1.1169</v>
+        <v>1.1084</v>
       </c>
       <c r="EH6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="EI6">
-        <v>3074</v>
+        <v>3335</v>
       </c>
       <c r="EJ6" t="s">
         <v>110</v>
@@ -5319,13 +5352,13 @@
         <v>112</v>
       </c>
       <c r="EL6">
-        <v>76.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="EM6">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="EN6">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="EO6">
         <v>0.8</v>
@@ -5334,46 +5367,46 @@
         <v>0</v>
       </c>
       <c r="EQ6">
-        <v>1.064</v>
+        <v>1.067</v>
       </c>
       <c r="ER6">
-        <v>77.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="ES6">
-        <v>74.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="ET6">
-        <v>62.7</v>
+        <v>63.2</v>
       </c>
       <c r="EU6">
-        <v>56.5</v>
+        <v>57.5</v>
       </c>
       <c r="EV6">
-        <v>47.4</v>
+        <v>43.2</v>
       </c>
       <c r="EW6">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="EX6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="EY6">
-        <v>8.800000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="EZ6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="FA6">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="FB6">
-        <v>94</v>
+        <v>95.5</v>
       </c>
       <c r="FC6">
         <v>10</v>
       </c>
       <c r="FD6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:160">
@@ -5390,43 +5423,43 @@
         <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J7">
-        <v>591.2</v>
+        <v>332.3</v>
       </c>
       <c r="K7">
-        <v>19.8</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>5</v>
       </c>
       <c r="M7">
-        <v>3.08</v>
+        <v>1.18</v>
       </c>
       <c r="N7">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P7">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -5435,25 +5468,25 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="U7">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="V7">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W7">
+        <v>4.5</v>
+      </c>
+      <c r="X7">
         <v>5.3</v>
       </c>
-      <c r="X7">
+      <c r="Y7">
         <v>6.1</v>
       </c>
-      <c r="Y7">
-        <v>7</v>
-      </c>
       <c r="Z7">
-        <v>96.5</v>
+        <v>66.7</v>
       </c>
       <c r="AA7">
         <v>0</v>
@@ -5468,49 +5501,49 @@
         <v>98.59999999999999</v>
       </c>
       <c r="AE7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AF7">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG7">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AH7">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AI7">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AJ7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AK7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN7">
         <v>1</v>
       </c>
       <c r="AO7">
-        <v>17.1</v>
+        <v>9.4</v>
       </c>
       <c r="AP7">
-        <v>85.8</v>
+        <v>88.7</v>
       </c>
       <c r="AQ7">
-        <v>70.8</v>
+        <v>70.5</v>
       </c>
       <c r="AR7">
         <v>0.78</v>
       </c>
       <c r="AS7">
-        <v>0.8159999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AT7">
         <v>10</v>
@@ -5537,238 +5570,238 @@
         <v>113</v>
       </c>
       <c r="BB7">
-        <v>91.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="BC7">
-        <v>85.90000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="BD7">
-        <v>51.3</v>
+        <v>51.9</v>
       </c>
       <c r="BE7">
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="BF7">
-        <v>993.2</v>
+        <v>993</v>
       </c>
       <c r="BG7">
-        <v>1011.1</v>
+        <v>1010.8</v>
       </c>
       <c r="BH7">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BI7">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="BJ7">
         <v>0</v>
       </c>
       <c r="BK7">
-        <v>115.4</v>
+        <v>140.3</v>
       </c>
       <c r="BL7">
         <v>0</v>
       </c>
       <c r="BM7">
+        <v>7</v>
+      </c>
+      <c r="BN7">
+        <v>5.7</v>
+      </c>
+      <c r="BO7">
+        <v>7.2</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>129</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>308</v>
+      </c>
+      <c r="BR7">
+        <v>0.14</v>
+      </c>
+      <c r="BS7">
+        <v>5.7</v>
+      </c>
+      <c r="BT7">
+        <v>7.2</v>
+      </c>
+      <c r="BU7">
+        <v>7.9</v>
+      </c>
+      <c r="BV7">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BW7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX7">
+        <v>2</v>
+      </c>
+      <c r="BY7">
+        <v>4.3</v>
+      </c>
+      <c r="BZ7">
+        <v>4.6</v>
+      </c>
+      <c r="CA7">
+        <v>2.7</v>
+      </c>
+      <c r="CB7">
+        <v>5.6</v>
+      </c>
+      <c r="CC7">
+        <v>6.1</v>
+      </c>
+      <c r="CD7">
+        <v>3.1</v>
+      </c>
+      <c r="CE7">
+        <v>6.3</v>
+      </c>
+      <c r="CF7">
+        <v>7</v>
+      </c>
+      <c r="CG7">
+        <v>3.6</v>
+      </c>
+      <c r="CH7">
+        <v>7.2</v>
+      </c>
+      <c r="CI7">
+        <v>8.1</v>
+      </c>
+      <c r="CJ7">
+        <v>3.9</v>
+      </c>
+      <c r="CK7">
+        <v>7.7</v>
+      </c>
+      <c r="CL7">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="CM7">
+        <v>3.6</v>
+      </c>
+      <c r="CN7">
+        <v>4.8</v>
+      </c>
+      <c r="CO7">
+        <v>5.4</v>
+      </c>
+      <c r="CP7">
+        <v>6.3</v>
+      </c>
+      <c r="CQ7">
+        <v>6.7</v>
+      </c>
+      <c r="CR7">
+        <v>7.2</v>
+      </c>
+      <c r="CS7">
+        <v>4.8</v>
+      </c>
+      <c r="CT7">
         <v>7.5</v>
       </c>
-      <c r="BN7">
-        <v>6.1</v>
-      </c>
-      <c r="BO7">
-        <v>7.7</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>128</v>
-      </c>
-      <c r="BQ7" t="s">
-        <v>307</v>
-      </c>
-      <c r="BR7">
-        <v>0.141</v>
-      </c>
-      <c r="BS7">
-        <v>6.1</v>
-      </c>
-      <c r="BT7">
-        <v>7.7</v>
-      </c>
-      <c r="BU7">
+      <c r="CU7">
+        <v>7.9</v>
+      </c>
+      <c r="CV7">
         <v>8.5</v>
       </c>
-      <c r="BV7">
-        <v>9.4</v>
-      </c>
-      <c r="BW7">
-        <v>9.9</v>
-      </c>
-      <c r="BX7">
-        <v>2.5</v>
-      </c>
-      <c r="BY7">
-        <v>4.8</v>
-      </c>
-      <c r="BZ7">
-        <v>4.9</v>
-      </c>
-      <c r="CA7">
-        <v>3.3</v>
-      </c>
-      <c r="CB7">
-        <v>6.2</v>
-      </c>
-      <c r="CC7">
-        <v>6.5</v>
-      </c>
-      <c r="CD7">
-        <v>3.8</v>
-      </c>
-      <c r="CE7">
-        <v>7</v>
-      </c>
-      <c r="CF7">
-        <v>7.4</v>
-      </c>
-      <c r="CG7">
-        <v>4.4</v>
-      </c>
-      <c r="CH7">
-        <v>8</v>
-      </c>
-      <c r="CI7">
-        <v>8.6</v>
-      </c>
-      <c r="CJ7">
-        <v>4.8</v>
-      </c>
-      <c r="CK7">
-        <v>8.6</v>
-      </c>
-      <c r="CL7">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="CM7">
-        <v>4.1</v>
-      </c>
-      <c r="CN7">
-        <v>5.4</v>
-      </c>
-      <c r="CO7">
-        <v>6.1</v>
-      </c>
-      <c r="CP7">
-        <v>7</v>
-      </c>
-      <c r="CQ7">
-        <v>7.6</v>
-      </c>
-      <c r="CR7">
-        <v>7.7</v>
-      </c>
-      <c r="CS7">
-        <v>5.4</v>
-      </c>
-      <c r="CT7">
-        <v>8</v>
-      </c>
-      <c r="CU7">
-        <v>8.5</v>
-      </c>
-      <c r="CV7">
+      <c r="CW7">
+        <v>5.7</v>
+      </c>
+      <c r="CX7">
+        <v>11.7</v>
+      </c>
+      <c r="CY7">
         <v>9.1</v>
       </c>
-      <c r="CW7">
-        <v>6.1</v>
-      </c>
-      <c r="CX7">
-        <v>13.4</v>
-      </c>
-      <c r="CY7">
-        <v>10.4</v>
-      </c>
       <c r="CZ7">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="DA7">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="DB7" t="s">
         <v>119</v>
       </c>
       <c r="DC7">
-        <v>230.9</v>
+        <v>234.9</v>
       </c>
       <c r="DD7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="DE7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="DF7">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="DG7">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="DH7">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="DI7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="DJ7">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="DK7">
+        <v>6.1</v>
+      </c>
+      <c r="DL7">
+        <v>3.1</v>
+      </c>
+      <c r="DM7">
         <v>6.9</v>
       </c>
-      <c r="DL7">
-        <v>3.8</v>
-      </c>
-      <c r="DM7">
-        <v>7.4</v>
-      </c>
       <c r="DN7">
+        <v>3.3</v>
+      </c>
+      <c r="DO7">
+        <v>5</v>
+      </c>
+      <c r="DP7">
+        <v>2.6</v>
+      </c>
+      <c r="DQ7">
+        <v>5.7</v>
+      </c>
+      <c r="DR7">
+        <v>6.1</v>
+      </c>
+      <c r="DS7">
         <v>3.1</v>
       </c>
-      <c r="DO7">
+      <c r="DT7">
+        <v>6.9</v>
+      </c>
+      <c r="DU7">
         <v>5.6</v>
       </c>
-      <c r="DP7">
-        <v>3.1</v>
-      </c>
-      <c r="DQ7">
-        <v>6</v>
-      </c>
-      <c r="DR7">
-        <v>6.9</v>
-      </c>
-      <c r="DS7">
-        <v>3.8</v>
-      </c>
-      <c r="DT7">
-        <v>7.4</v>
-      </c>
-      <c r="DU7">
-        <v>6.3</v>
-      </c>
       <c r="DV7">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="DW7">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="DX7">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="DY7">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="DZ7">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="EA7">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="EB7">
         <v>0.7</v>
@@ -5786,13 +5819,13 @@
         <v>0.12</v>
       </c>
       <c r="EG7">
-        <v>1.1253</v>
+        <v>1.1203</v>
       </c>
       <c r="EH7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="EI7">
-        <v>2799</v>
+        <v>2958</v>
       </c>
       <c r="EJ7" t="s">
         <v>110</v>
@@ -5801,61 +5834,61 @@
         <v>112</v>
       </c>
       <c r="EL7">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="EM7">
+        <v>10</v>
+      </c>
+      <c r="EN7">
+        <v>11.8</v>
+      </c>
+      <c r="EO7">
+        <v>0.5</v>
+      </c>
+      <c r="EP7">
+        <v>0</v>
+      </c>
+      <c r="EQ7">
+        <v>1.056</v>
+      </c>
+      <c r="ER7">
         <v>74.3</v>
       </c>
-      <c r="EM7">
-        <v>9.5</v>
-      </c>
-      <c r="EN7">
-        <v>13.3</v>
-      </c>
-      <c r="EO7">
-        <v>0.7</v>
-      </c>
-      <c r="EP7">
-        <v>0</v>
-      </c>
-      <c r="EQ7">
-        <v>1.058</v>
-      </c>
-      <c r="ER7">
-        <v>75.3</v>
-      </c>
       <c r="ES7">
-        <v>72.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="ET7">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
       <c r="EU7">
-        <v>55.6</v>
+        <v>55.8</v>
       </c>
       <c r="EV7">
-        <v>51.8</v>
+        <v>49.3</v>
       </c>
       <c r="EW7">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="EX7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="EY7">
-        <v>11.9</v>
+        <v>12.8</v>
       </c>
       <c r="EZ7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="FA7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="FB7">
-        <v>90</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="FC7">
         <v>10</v>
       </c>
       <c r="FD7">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="8" spans="1:160">
@@ -5872,130 +5905,130 @@
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J8">
-        <v>591.2</v>
+        <v>332.3</v>
       </c>
       <c r="K8">
-        <v>20.8</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <v>5</v>
       </c>
       <c r="M8">
-        <v>3.35</v>
+        <v>2.21</v>
       </c>
       <c r="N8">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="O8">
         <v>0.5</v>
       </c>
       <c r="P8">
-        <v>29.7</v>
+        <v>28.3</v>
       </c>
       <c r="Q8">
+        <v>1.3</v>
+      </c>
+      <c r="R8">
+        <v>25</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>4.9</v>
+      </c>
+      <c r="U8">
+        <v>5.7</v>
+      </c>
+      <c r="V8">
+        <v>6.6</v>
+      </c>
+      <c r="W8">
+        <v>0.7</v>
+      </c>
+      <c r="X8">
+        <v>2.7</v>
+      </c>
+      <c r="Y8">
+        <v>4.2</v>
+      </c>
+      <c r="Z8">
+        <v>1.1</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>99.7</v>
+      </c>
+      <c r="AD8">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF8">
         <v>0.9</v>
       </c>
-      <c r="R8">
-        <v>81.2</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>5.2</v>
-      </c>
-      <c r="U8">
-        <v>6.3</v>
-      </c>
-      <c r="V8">
-        <v>7.6</v>
-      </c>
-      <c r="W8">
-        <v>2.7</v>
-      </c>
-      <c r="X8">
-        <v>4.3</v>
-      </c>
-      <c r="Y8">
-        <v>5.6</v>
-      </c>
-      <c r="Z8">
-        <v>24.5</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>100</v>
-      </c>
-      <c r="AD8">
-        <v>97.5</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF8">
-        <v>1.5</v>
-      </c>
       <c r="AG8">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="AH8">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="AI8">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="AJ8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AK8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN8">
         <v>1</v>
       </c>
       <c r="AO8">
-        <v>17.4</v>
+        <v>13.7</v>
       </c>
       <c r="AP8">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="AQ8">
-        <v>65.5</v>
+        <v>64.2</v>
       </c>
       <c r="AR8">
         <v>0.78</v>
       </c>
       <c r="AS8">
-        <v>0.8159999999999999</v>
+        <v>0.824</v>
       </c>
       <c r="AT8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU8">
         <v>0</v>
@@ -6019,34 +6052,34 @@
         <v>113</v>
       </c>
       <c r="BB8">
-        <v>88</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="BC8">
-        <v>84.5</v>
+        <v>85.3</v>
       </c>
       <c r="BD8">
-        <v>55.2</v>
+        <v>52.5</v>
       </c>
       <c r="BE8">
-        <v>34.3</v>
+        <v>31.1</v>
       </c>
       <c r="BF8">
-        <v>993.6</v>
+        <v>993.7</v>
       </c>
       <c r="BG8">
         <v>1011.7</v>
       </c>
       <c r="BH8">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="BI8">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="BJ8">
         <v>0</v>
       </c>
       <c r="BK8">
-        <v>93.8</v>
+        <v>133.1</v>
       </c>
       <c r="BL8">
         <v>0</v>
@@ -6055,202 +6088,202 @@
         <v>5.1</v>
       </c>
       <c r="BN8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO8">
         <v>5.2</v>
       </c>
       <c r="BP8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BQ8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BR8">
-        <v>0.141</v>
+        <v>0.14</v>
       </c>
       <c r="BS8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT8">
         <v>5.2</v>
       </c>
       <c r="BU8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV8">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="BW8">
         <v>6.7</v>
       </c>
       <c r="BX8">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="BY8">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="BZ8">
         <v>3.3</v>
       </c>
       <c r="CA8">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="CB8">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="CC8">
         <v>4.4</v>
       </c>
       <c r="CD8">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="CE8">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="CF8">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CG8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CH8">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="CI8">
         <v>5.8</v>
       </c>
       <c r="CJ8">
+        <v>1.1</v>
+      </c>
+      <c r="CK8">
+        <v>4.5</v>
+      </c>
+      <c r="CL8">
+        <v>6.3</v>
+      </c>
+      <c r="CM8">
+        <v>1.8</v>
+      </c>
+      <c r="CN8">
+        <v>2.4</v>
+      </c>
+      <c r="CO8">
+        <v>2.8</v>
+      </c>
+      <c r="CP8">
         <v>3.3</v>
       </c>
-      <c r="CK8">
-        <v>5.8</v>
-      </c>
-      <c r="CL8">
-        <v>6.2</v>
-      </c>
-      <c r="CM8">
-        <v>2.8</v>
-      </c>
-      <c r="CN8">
-        <v>3.6</v>
-      </c>
-      <c r="CO8">
-        <v>4.2</v>
-      </c>
-      <c r="CP8">
-        <v>4.8</v>
-      </c>
       <c r="CQ8">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="CR8">
         <v>5.2</v>
       </c>
       <c r="CS8">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="CT8">
         <v>5.4</v>
       </c>
       <c r="CU8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="CV8">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="CW8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="CX8">
-        <v>10.9</v>
+        <v>8.5</v>
       </c>
       <c r="CY8">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="CZ8">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="DA8">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="DB8" t="s">
-        <v>119</v>
+        <v>309</v>
       </c>
       <c r="DC8">
-        <v>230.6</v>
+        <v>251.5</v>
       </c>
       <c r="DD8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="DE8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="DF8">
-        <v>80.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="DG8">
-        <v>80.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="DH8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="DI8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="DJ8">
-        <v>1.2</v>
+        <v>16.1</v>
       </c>
       <c r="DK8">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="DL8">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="DM8">
         <v>5</v>
       </c>
       <c r="DN8">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="DO8">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="DP8">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="DQ8">
         <v>4.1</v>
       </c>
       <c r="DR8">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="DS8">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="DT8">
         <v>5</v>
       </c>
       <c r="DU8">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="DV8">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="DW8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="DX8">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="DY8">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="DZ8">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="EA8">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="EB8">
         <v>0.5</v>
@@ -6268,13 +6301,13 @@
         <v>0.12</v>
       </c>
       <c r="EG8">
-        <v>1.1312</v>
+        <v>1.129</v>
       </c>
       <c r="EH8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="EI8">
-        <v>2584</v>
+        <v>2672</v>
       </c>
       <c r="EJ8" t="s">
         <v>110</v>
@@ -6283,61 +6316,61 @@
         <v>112</v>
       </c>
       <c r="EL8">
-        <v>69.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="EM8">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="EN8">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="EO8">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="EP8">
         <v>0</v>
       </c>
       <c r="EQ8">
-        <v>1.047</v>
+        <v>1.039</v>
       </c>
       <c r="ER8">
-        <v>70.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="ES8">
-        <v>68.2</v>
+        <v>64.8</v>
       </c>
       <c r="ET8">
-        <v>59.1</v>
+        <v>59.4</v>
       </c>
       <c r="EU8">
-        <v>54.6</v>
+        <v>54</v>
       </c>
       <c r="EV8">
-        <v>55.1</v>
+        <v>53.7</v>
       </c>
       <c r="EW8">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="EX8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="EY8">
-        <v>22.2</v>
+        <v>12.9</v>
       </c>
       <c r="EZ8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="FA8">
         <v>88</v>
       </c>
       <c r="FB8">
-        <v>85.5</v>
+        <v>87.8</v>
       </c>
       <c r="FC8">
         <v>10</v>
       </c>
       <c r="FD8">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9" spans="1:160">
@@ -6354,43 +6387,43 @@
         <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J9">
-        <v>591.2</v>
+        <v>332.3</v>
       </c>
       <c r="K9">
-        <v>21.8</v>
+        <v>3</v>
       </c>
       <c r="L9">
         <v>5</v>
       </c>
       <c r="M9">
-        <v>3.29</v>
+        <v>2.19</v>
       </c>
       <c r="N9">
-        <v>1.38</v>
+        <v>0.6</v>
       </c>
       <c r="O9">
         <v>0.5</v>
       </c>
       <c r="P9">
-        <v>74.90000000000001</v>
+        <v>42.6</v>
       </c>
       <c r="Q9">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="R9">
         <v>25</v>
@@ -6399,85 +6432,85 @@
         <v>18.8</v>
       </c>
       <c r="T9">
+        <v>2.6</v>
+      </c>
+      <c r="U9">
+        <v>3.6</v>
+      </c>
+      <c r="V9">
+        <v>4.6</v>
+      </c>
+      <c r="W9">
+        <v>-0.4</v>
+      </c>
+      <c r="X9">
         <v>0.1</v>
       </c>
-      <c r="U9">
-        <v>1.3</v>
-      </c>
-      <c r="V9">
-        <v>2.8</v>
-      </c>
-      <c r="W9">
-        <v>-1.4</v>
-      </c>
-      <c r="X9">
-        <v>-0.3</v>
-      </c>
       <c r="Y9">
+        <v>1.2</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>60.4</v>
+      </c>
+      <c r="AD9">
+        <v>58.8</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF9">
         <v>0.1</v>
       </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>15.5</v>
-      </c>
-      <c r="AD9">
-        <v>83</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF9">
-        <v>-0.2</v>
-      </c>
       <c r="AG9">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AH9">
-        <v>-0.6</v>
+        <v>0.3</v>
       </c>
       <c r="AI9">
-        <v>-0.7</v>
+        <v>0.3</v>
       </c>
       <c r="AJ9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AK9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN9">
         <v>1</v>
       </c>
       <c r="AO9">
-        <v>17.5</v>
+        <v>10.7</v>
       </c>
       <c r="AP9">
-        <v>87.8</v>
+        <v>92.3</v>
       </c>
       <c r="AQ9">
-        <v>58.1</v>
+        <v>59.1</v>
       </c>
       <c r="AR9">
         <v>0.78</v>
       </c>
       <c r="AS9">
-        <v>0.746</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="AT9">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU9">
         <v>0</v>
@@ -6501,178 +6534,178 @@
         <v>113</v>
       </c>
       <c r="BB9">
-        <v>85.7</v>
+        <v>88</v>
       </c>
       <c r="BC9">
-        <v>82.2</v>
+        <v>83</v>
       </c>
       <c r="BD9">
-        <v>55.2</v>
+        <v>52</v>
       </c>
       <c r="BE9">
-        <v>37.3</v>
+        <v>33.3</v>
       </c>
       <c r="BF9">
-        <v>994</v>
+        <v>993.7</v>
       </c>
       <c r="BG9">
-        <v>1012.1</v>
+        <v>1011.8</v>
       </c>
       <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>1.6</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>139.8</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
         <v>2.8</v>
       </c>
-      <c r="BI9">
+      <c r="BN9">
+        <v>2.3</v>
+      </c>
+      <c r="BO9">
+        <v>2.8</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>129</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>308</v>
+      </c>
+      <c r="BR9">
+        <v>0.141</v>
+      </c>
+      <c r="BS9">
+        <v>2.3</v>
+      </c>
+      <c r="BT9">
+        <v>2.8</v>
+      </c>
+      <c r="BU9">
+        <v>3.1</v>
+      </c>
+      <c r="BV9">
+        <v>3.5</v>
+      </c>
+      <c r="BW9">
+        <v>3.7</v>
+      </c>
+      <c r="BX9">
+        <v>-0.9</v>
+      </c>
+      <c r="BY9">
+        <v>0.2</v>
+      </c>
+      <c r="BZ9">
+        <v>1.2</v>
+      </c>
+      <c r="CA9">
+        <v>-1.2</v>
+      </c>
+      <c r="CB9">
         <v>0.3</v>
       </c>
-      <c r="BJ9">
-        <v>0</v>
-      </c>
-      <c r="BK9">
-        <v>87.7</v>
-      </c>
-      <c r="BL9">
-        <v>0</v>
-      </c>
-      <c r="BM9">
-        <v>0</v>
-      </c>
-      <c r="BN9">
-        <v>0</v>
-      </c>
-      <c r="BO9">
-        <v>0</v>
-      </c>
-      <c r="BP9" t="s">
-        <v>128</v>
-      </c>
-      <c r="BQ9" t="s">
-        <v>307</v>
-      </c>
-      <c r="BR9">
-        <v>0.149</v>
-      </c>
-      <c r="BS9">
-        <v>0</v>
-      </c>
-      <c r="BT9">
-        <v>0</v>
-      </c>
-      <c r="BU9">
-        <v>0</v>
-      </c>
-      <c r="BV9">
-        <v>0</v>
-      </c>
-      <c r="BW9">
-        <v>0</v>
-      </c>
-      <c r="BX9">
-        <v>-0</v>
-      </c>
-      <c r="BY9">
-        <v>-0</v>
-      </c>
-      <c r="BZ9">
-        <v>-0</v>
-      </c>
-      <c r="CA9">
-        <v>-0</v>
-      </c>
-      <c r="CB9">
-        <v>-0</v>
-      </c>
       <c r="CC9">
-        <v>-0</v>
+        <v>1.6</v>
       </c>
       <c r="CD9">
-        <v>-0</v>
+        <v>-1.3</v>
       </c>
       <c r="CE9">
-        <v>-0</v>
+        <v>0.3</v>
       </c>
       <c r="CF9">
-        <v>-0</v>
+        <v>1.8</v>
       </c>
       <c r="CG9">
-        <v>-0</v>
+        <v>-1.5</v>
       </c>
       <c r="CH9">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="CI9">
-        <v>-0</v>
+        <v>2.1</v>
       </c>
       <c r="CJ9">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
       <c r="CK9">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="CL9">
-        <v>-0</v>
+        <v>2.3</v>
       </c>
       <c r="CM9">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="CN9">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="CO9">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="CP9">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="CQ9">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="CR9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="CS9">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="CT9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CU9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="CV9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="CW9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="CX9">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="CY9">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="CZ9">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="DA9">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="DB9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="DC9">
-        <v>336.2</v>
+        <v>290.2</v>
       </c>
       <c r="DD9" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="DE9" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="DF9">
-        <v>29.9</v>
+        <v>62.1</v>
       </c>
       <c r="DG9">
-        <v>29.9</v>
+        <v>62.1</v>
       </c>
       <c r="DH9">
         <v>0</v>
@@ -6684,58 +6717,58 @@
         <v>0</v>
       </c>
       <c r="DK9">
-        <v>-0</v>
+        <v>0.3</v>
       </c>
       <c r="DL9">
-        <v>-0</v>
+        <v>-1.3</v>
       </c>
       <c r="DM9">
-        <v>-0</v>
+        <v>1.8</v>
       </c>
       <c r="DN9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="DO9">
-        <v>-0</v>
+        <v>0.2</v>
       </c>
       <c r="DP9">
-        <v>-0</v>
+        <v>-1.1</v>
       </c>
       <c r="DQ9">
-        <v>-0</v>
+        <v>1.5</v>
       </c>
       <c r="DR9">
-        <v>-0</v>
+        <v>0.3</v>
       </c>
       <c r="DS9">
-        <v>-0</v>
+        <v>-1.3</v>
       </c>
       <c r="DT9">
-        <v>-0</v>
+        <v>1.8</v>
       </c>
       <c r="DU9">
-        <v>-0</v>
+        <v>0.3</v>
       </c>
       <c r="DV9">
-        <v>-0</v>
+        <v>-1.2</v>
       </c>
       <c r="DW9">
-        <v>-0</v>
+        <v>1.6</v>
       </c>
       <c r="DX9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="DY9">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="DZ9">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="EA9">
-        <v>1</v>
+        <v>0.37</v>
       </c>
       <c r="EB9">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="EC9">
         <v>0.85</v>
@@ -6750,13 +6783,13 @@
         <v>0.12</v>
       </c>
       <c r="EG9">
-        <v>1.1364</v>
+        <v>1.1319</v>
       </c>
       <c r="EH9" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="EI9">
-        <v>2419</v>
+        <v>2582</v>
       </c>
       <c r="EJ9" t="s">
         <v>110</v>
@@ -6765,13 +6798,13 @@
         <v>112</v>
       </c>
       <c r="EL9">
-        <v>59.2</v>
+        <v>59.9</v>
       </c>
       <c r="EM9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="EN9">
-        <v>-0</v>
+        <v>0.2</v>
       </c>
       <c r="EO9">
         <v>0</v>
@@ -6780,46 +6813,46 @@
         <v>0</v>
       </c>
       <c r="EQ9">
-        <v>1.022</v>
+        <v>1.024</v>
       </c>
       <c r="ER9">
-        <v>59.2</v>
+        <v>61.3</v>
       </c>
       <c r="ES9">
-        <v>59.2</v>
+        <v>58.7</v>
       </c>
       <c r="ET9">
-        <v>54.6</v>
+        <v>56.6</v>
       </c>
       <c r="EU9">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
       <c r="EV9">
-        <v>57.7</v>
+        <v>55.1</v>
       </c>
       <c r="EW9">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="EX9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="EY9">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="EZ9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="FA9">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="FB9">
-        <v>82.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="FC9">
         <v>0</v>
       </c>
       <c r="FD9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>
@@ -6921,22 +6954,22 @@
         <v>109</v>
       </c>
       <c r="E2">
-        <v>63.8</v>
+        <v>64.2</v>
       </c>
       <c r="F2" t="s">
         <v>121</v>
       </c>
       <c r="G2">
-        <v>86.3</v>
+        <v>88.7</v>
       </c>
       <c r="H2">
         <v>9</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -6945,16 +6978,16 @@
         <v>124</v>
       </c>
       <c r="M2">
-        <v>91.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="N2">
-        <v>2815</v>
+        <v>2999</v>
       </c>
       <c r="O2" t="s">
         <v>110</v>
       </c>
       <c r="P2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -6974,13 +7007,13 @@
         <v>108</v>
       </c>
       <c r="E3">
-        <v>63</v>
+        <v>62.7</v>
       </c>
       <c r="F3" t="s">
         <v>121</v>
       </c>
       <c r="G3">
-        <v>94.7</v>
+        <v>89</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -6989,7 +7022,7 @@
         <v>6</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -6998,16 +7031,16 @@
         <v>124</v>
       </c>
       <c r="M3">
-        <v>64.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="N3">
-        <v>978</v>
+        <v>1015</v>
       </c>
       <c r="O3" t="s">
         <v>110</v>
       </c>
       <c r="P3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q3">
         <v>5</v>
